--- a/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output1.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output1.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45232.58388888889</v>
+        <v>46116.3550925926</v>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,39 +502,39 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45232.69068287037</v>
+        <v>46116.52167824074</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3" t="n">
         <v>40</v>
       </c>
-      <c r="D3" t="n">
-        <v>29</v>
-      </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -545,19 +545,19 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45232.81658564815</v>
+        <v>46116.69474537037</v>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
+        <v>74</v>
+      </c>
+      <c r="D4" t="n">
         <v>40</v>
       </c>
-      <c r="D4" t="n">
-        <v>30</v>
-      </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -582,19 +582,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45232.939375</v>
+        <v>46116.85944444445</v>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -619,19 +619,19 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45233.06450231482</v>
+        <v>46117.03664351852</v>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -645,39 +645,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45233.19976851852</v>
+        <v>46117.24065972222</v>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -693,33 +693,33 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45233.3163425926</v>
+        <v>46117.36049768519</v>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -730,33 +730,33 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45233.44524305555</v>
+        <v>46117.52633101852</v>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -767,33 +767,33 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45233.5778125</v>
+        <v>46117.69008101852</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -804,19 +804,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45233.70393518519</v>
+        <v>46117.87108796297</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -841,56 +841,56 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45233.81425925926</v>
+        <v>46118.0265625</v>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45233.94961805556</v>
+        <v>46118.19368055555</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -899,12 +899,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -915,19 +915,19 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45234.07908564815</v>
+        <v>46118.36050925926</v>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
+        <v>76</v>
+      </c>
+      <c r="D14" t="n">
         <v>39</v>
       </c>
-      <c r="D14" t="n">
-        <v>29</v>
-      </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -941,30 +941,30 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45234.205625</v>
+        <v>46118.52253472222</v>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -983,29 +983,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45234.32534722222</v>
+        <v>46118.68907407407</v>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1026,23 +1026,23 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45234.44539351852</v>
+        <v>46118.8552662037</v>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1063,19 +1063,19 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45234.57993055556</v>
+        <v>46119.02732638889</v>
       </c>
       <c r="B18" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1100,19 +1100,19 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45234.69010416666</v>
+        <v>46120.18833333333</v>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1137,19 +1137,19 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45234.8234837963</v>
+        <v>46120.52369212963</v>
       </c>
       <c r="B20" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C20" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1174,19 +1174,19 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45234.94009259259</v>
+        <v>46120.69190972222</v>
       </c>
       <c r="B21" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45235.07965277778</v>
+        <v>46120.85443287037</v>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C22" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1237,30 +1237,30 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45235.1914699074</v>
+        <v>46124.39263888889</v>
       </c>
       <c r="B23" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1269,35 +1269,35 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45235.31483796296</v>
+        <v>46124.52407407408</v>
       </c>
       <c r="B24" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1322,19 +1322,19 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45235.4407175926</v>
+        <v>46124.69166666667</v>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C25" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1348,30 +1348,30 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45235.56414351852</v>
+        <v>46124.85614583334</v>
       </c>
       <c r="B26" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C26" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1396,19 +1396,19 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45235.70108796296</v>
+        <v>46125.07673611111</v>
       </c>
       <c r="B27" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E27" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1433,19 +1433,19 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45235.81854166667</v>
+        <v>46125.18878472222</v>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45235.94466435185</v>
+        <v>46125.37304398148</v>
       </c>
       <c r="B29" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1501,66 +1501,66 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45236.22508101852</v>
+        <v>46125.52486111111</v>
       </c>
       <c r="B30" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C30" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45236.31480324074</v>
+        <v>46125.69287037037</v>
       </c>
       <c r="B31" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1570,30 +1570,30 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45236.44541666667</v>
+        <v>46125.85716435185</v>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C32" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E32" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1602,35 +1602,35 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45236.5659837963</v>
+        <v>46126.03134259259</v>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C33" t="n">
+        <v>77</v>
+      </c>
+      <c r="D33" t="n">
         <v>37</v>
       </c>
-      <c r="D33" t="n">
-        <v>31</v>
-      </c>
       <c r="E33" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45236.6902662037</v>
+        <v>46126.21274305556</v>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E34" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1681,30 +1681,30 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45236.81527777778</v>
+        <v>46126.35861111111</v>
       </c>
       <c r="B35" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C35" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1723,140 +1723,140 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45236.9453125</v>
+        <v>46126.53461805556</v>
       </c>
       <c r="B36" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C36" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45237.06493055556</v>
+        <v>46126.70118055555</v>
       </c>
       <c r="B37" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C37" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45237.19125</v>
+        <v>46126.87692129629</v>
       </c>
       <c r="B38" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C38" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E38" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45237.3155787037</v>
+        <v>46127.02172453704</v>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1866,34 +1866,34 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45237.44138888889</v>
+        <v>46127.20758101852</v>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C40" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="D40" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1903,34 +1903,34 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45237.57152777778</v>
+        <v>46127.35572916667</v>
       </c>
       <c r="B41" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C41" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E41" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1951,60 +1951,60 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45237.69288194444</v>
+        <v>46127.53050925926</v>
       </c>
       <c r="B42" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C42" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D42" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E42" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45237.82814814815</v>
+        <v>46127.69168981481</v>
       </c>
       <c r="B43" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D43" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E43" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2014,30 +2014,30 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45237.94748842593</v>
+        <v>46127.85546296297</v>
       </c>
       <c r="B44" t="n">
+        <v>52</v>
+      </c>
+      <c r="C44" t="n">
+        <v>74</v>
+      </c>
+      <c r="D44" t="n">
         <v>33</v>
       </c>
-      <c r="C44" t="n">
-        <v>41</v>
-      </c>
-      <c r="D44" t="n">
-        <v>31</v>
-      </c>
       <c r="E44" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2046,81 +2046,81 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45238.07994212963</v>
+        <v>46128.04122685185</v>
       </c>
       <c r="B45" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D45" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E45" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45238.2062037037</v>
+        <v>46128.19846064815</v>
       </c>
       <c r="B46" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D46" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2130,25 +2130,25 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45238.31596064815</v>
+        <v>46128.3578125</v>
       </c>
       <c r="B47" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="D47" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2173,278 +2173,278 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45238.44385416667</v>
+        <v>46128.52149305555</v>
       </c>
       <c r="B48" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D48" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45238.56461805556</v>
+        <v>46128.69186342593</v>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C49" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="D49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45238.70608796296</v>
+        <v>46128.85454861111</v>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C50" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E50" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45238.81765046297</v>
+        <v>46129.08709490741</v>
       </c>
       <c r="B51" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C51" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E51" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45238.94136574074</v>
+        <v>46129.20550925926</v>
       </c>
       <c r="B52" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C52" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D52" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E52" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45239.07863425926</v>
+        <v>46129.36481481481</v>
       </c>
       <c r="B53" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C53" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E53" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45239.20971064815</v>
+        <v>46129.52703703703</v>
       </c>
       <c r="B54" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C54" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E54" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45239.31733796297</v>
+        <v>46129.69325231481</v>
       </c>
       <c r="B55" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C55" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D55" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2453,35 +2453,35 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45239.44678240741</v>
+        <v>46129.85914351852</v>
       </c>
       <c r="B56" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C56" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="D56" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2490,35 +2490,35 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45239.56444444445</v>
+        <v>46130.09744212963</v>
       </c>
       <c r="B57" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C57" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="D57" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2527,35 +2527,35 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45239.69660879629</v>
+        <v>46130.19385416667</v>
       </c>
       <c r="B58" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C58" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D58" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2569,30 +2569,30 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45239.81575231482</v>
+        <v>46130.35618055556</v>
       </c>
       <c r="B59" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C59" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E59" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2601,35 +2601,35 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45239.96009259259</v>
+        <v>46130.52403935185</v>
       </c>
       <c r="B60" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C60" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E60" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2643,34 +2643,34 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45240.07539351852</v>
+        <v>46131.02777777778</v>
       </c>
       <c r="B61" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C61" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D61" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E61" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2680,34 +2680,34 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45240.32247685185</v>
+        <v>46131.35472222222</v>
       </c>
       <c r="B62" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C62" t="n">
+        <v>72</v>
+      </c>
+      <c r="D62" t="n">
         <v>35</v>
       </c>
-      <c r="D62" t="n">
-        <v>29</v>
-      </c>
       <c r="E62" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2717,67 +2717,67 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45240.45472222222</v>
+        <v>46131.52929398148</v>
       </c>
       <c r="B63" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C63" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E63" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45240.56987268518</v>
+        <v>46131.68760416667</v>
       </c>
       <c r="B64" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C64" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D64" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E64" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2786,39 +2786,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45240.69065972222</v>
+        <v>46132.02103009259</v>
       </c>
       <c r="B65" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C65" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D65" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E65" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2828,71 +2828,71 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45240.81402777778</v>
+        <v>46132.19717592592</v>
       </c>
       <c r="B66" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C66" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D66" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E66" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45240.93924768519</v>
+        <v>46132.3584375</v>
       </c>
       <c r="B67" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C67" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D67" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E67" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2902,108 +2902,108 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45241.06414351852</v>
+        <v>46132.52159722222</v>
       </c>
       <c r="B68" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C68" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D68" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45241.19800925926</v>
+        <v>46132.69394675926</v>
       </c>
       <c r="B69" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C69" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D69" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E69" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45241.33342592593</v>
+        <v>46132.86247685185</v>
       </c>
       <c r="B70" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C70" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="D70" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E70" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3013,34 +3013,34 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45241.45502314815</v>
+        <v>46133.07111111111</v>
       </c>
       <c r="B71" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C71" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D71" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3050,34 +3050,34 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45241.56454861111</v>
+        <v>46133.19524305555</v>
       </c>
       <c r="B72" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C72" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="D72" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3087,34 +3087,34 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45241.70119212963</v>
+        <v>46133.36118055556</v>
       </c>
       <c r="B73" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C73" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D73" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E73" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3124,34 +3124,34 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45241.83112268519</v>
+        <v>46133.52528935186</v>
       </c>
       <c r="B74" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C74" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D74" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E74" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3161,330 +3161,330 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45241.9537037037</v>
+        <v>46133.69530092592</v>
       </c>
       <c r="B75" t="n">
+        <v>50</v>
+      </c>
+      <c r="C75" t="n">
+        <v>73</v>
+      </c>
+      <c r="D75" t="n">
         <v>34</v>
       </c>
-      <c r="C75" t="n">
-        <v>41</v>
-      </c>
-      <c r="D75" t="n">
-        <v>31</v>
-      </c>
       <c r="E75" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45242.08201388889</v>
+        <v>46133.85505787037</v>
       </c>
       <c r="B76" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C76" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D76" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E76" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45242.31623842593</v>
+        <v>46134.09811342593</v>
       </c>
       <c r="B77" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C77" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D77" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E77" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45242.4415625</v>
+        <v>46134.21712962963</v>
       </c>
       <c r="B78" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C78" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D78" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E78" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45242.56987268518</v>
+        <v>46134.35688657407</v>
       </c>
       <c r="B79" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C79" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D79" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E79" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45242.69986111111</v>
+        <v>46134.52453703704</v>
       </c>
       <c r="B80" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C80" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D80" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E80" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45242.81715277778</v>
+        <v>46134.72311342593</v>
       </c>
       <c r="B81" t="n">
+        <v>49</v>
+      </c>
+      <c r="C81" t="n">
+        <v>71</v>
+      </c>
+      <c r="D81" t="n">
         <v>33</v>
       </c>
-      <c r="C81" t="n">
-        <v>39</v>
-      </c>
-      <c r="D81" t="n">
-        <v>31</v>
-      </c>
       <c r="E81" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45242.93877314815</v>
+        <v>46134.85905092592</v>
       </c>
       <c r="B82" t="n">
+        <v>49</v>
+      </c>
+      <c r="C82" t="n">
+        <v>71</v>
+      </c>
+      <c r="D82" t="n">
         <v>33</v>
       </c>
-      <c r="C82" t="n">
-        <v>39</v>
-      </c>
-      <c r="D82" t="n">
-        <v>31</v>
-      </c>
       <c r="E82" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45243.08626157408</v>
+        <v>46135.02693287037</v>
       </c>
       <c r="B83" t="n">
+        <v>49</v>
+      </c>
+      <c r="C83" t="n">
+        <v>75</v>
+      </c>
+      <c r="D83" t="n">
         <v>33</v>
       </c>
-      <c r="C83" t="n">
-        <v>39</v>
-      </c>
-      <c r="D83" t="n">
-        <v>31</v>
-      </c>
       <c r="E83" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3494,30 +3494,30 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45243.31465277778</v>
+        <v>46135.3603125</v>
       </c>
       <c r="B84" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C84" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="D84" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3531,30 +3531,30 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45243.43993055556</v>
+        <v>46135.53359953704</v>
       </c>
       <c r="B85" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C85" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="D85" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3568,67 +3568,67 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45243.56521990741</v>
+        <v>46135.68820601852</v>
       </c>
       <c r="B86" t="n">
+        <v>49</v>
+      </c>
+      <c r="C86" t="n">
+        <v>71</v>
+      </c>
+      <c r="D86" t="n">
         <v>34</v>
       </c>
-      <c r="C86" t="n">
-        <v>36</v>
-      </c>
-      <c r="D86" t="n">
-        <v>33</v>
-      </c>
       <c r="E86" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45243.69731481482</v>
+        <v>46135.86390046297</v>
       </c>
       <c r="B87" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C87" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D87" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E87" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3642,30 +3642,30 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45243.85986111111</v>
+        <v>46136.02126157407</v>
       </c>
       <c r="B88" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C88" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D88" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E88" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3679,30 +3679,30 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45244.03325231482</v>
+        <v>46136.18943287037</v>
       </c>
       <c r="B89" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C89" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D89" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E89" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3716,30 +3716,30 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45244.20384259259</v>
+        <v>46136.35768518518</v>
       </c>
       <c r="B90" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C90" t="n">
+        <v>72</v>
+      </c>
+      <c r="D90" t="n">
         <v>37</v>
       </c>
-      <c r="D90" t="n">
-        <v>33</v>
-      </c>
       <c r="E90" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3758,214 +3758,214 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45244.36030092592</v>
+        <v>46136.52224537037</v>
       </c>
       <c r="B91" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C91" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="D91" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E91" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45244.52890046296</v>
+        <v>46136.6883912037</v>
       </c>
       <c r="B92" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C92" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D92" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E92" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45244.70230324074</v>
+        <v>46136.85456018519</v>
       </c>
       <c r="B93" t="n">
+        <v>49</v>
+      </c>
+      <c r="C93" t="n">
+        <v>70</v>
+      </c>
+      <c r="D93" t="n">
         <v>34</v>
       </c>
-      <c r="C93" t="n">
-        <v>40</v>
-      </c>
-      <c r="D93" t="n">
-        <v>31</v>
-      </c>
       <c r="E93" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45244.85921296296</v>
+        <v>46137.0588425926</v>
       </c>
       <c r="B94" t="n">
+        <v>49</v>
+      </c>
+      <c r="C94" t="n">
+        <v>70</v>
+      </c>
+      <c r="D94" t="n">
         <v>34</v>
       </c>
-      <c r="C94" t="n">
-        <v>38</v>
-      </c>
-      <c r="D94" t="n">
-        <v>31</v>
-      </c>
       <c r="E94" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45245.02326388889</v>
+        <v>46137.18950231482</v>
       </c>
       <c r="B95" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C95" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D95" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E95" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45245.20512731482</v>
+        <v>46137.36697916667</v>
       </c>
       <c r="B96" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C96" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D96" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3975,30 +3975,30 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45245.35769675926</v>
+        <v>46137.52636574074</v>
       </c>
       <c r="B97" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C97" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D97" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E97" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4007,35 +4007,35 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45245.5274537037</v>
+        <v>46137.68905092592</v>
       </c>
       <c r="B98" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C98" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D98" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E98" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4044,294 +4044,294 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45245.69355324074</v>
+        <v>46137.8555787037</v>
       </c>
       <c r="B99" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C99" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D99" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E99" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45246.03002314815</v>
+        <v>46138.08900462963</v>
       </c>
       <c r="B100" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C100" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D100" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E100" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>45246.21109953704</v>
+        <v>46138.22342592593</v>
       </c>
       <c r="B101" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C101" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D101" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E101" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>45246.35756944444</v>
+        <v>46138.35784722222</v>
       </c>
       <c r="B102" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C102" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D102" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E102" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>45246.52885416667</v>
+        <v>46138.54626157408</v>
       </c>
       <c r="B103" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C103" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D103" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E103" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>45246.70027777777</v>
+        <v>46138.69407407408</v>
       </c>
       <c r="B104" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C104" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D104" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E104" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>45246.85549768519</v>
+        <v>46138.85946759259</v>
       </c>
       <c r="B105" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C105" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D105" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E105" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>45247.03329861111</v>
+        <v>46139.04685185185</v>
       </c>
       <c r="B106" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C106" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D106" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E106" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4345,30 +4345,30 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45247.35915509259</v>
+        <v>46139.20314814815</v>
       </c>
       <c r="B107" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C107" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D107" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E107" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4382,104 +4382,104 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>45247.53670138889</v>
+        <v>46139.35634259259</v>
       </c>
       <c r="B108" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C108" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D108" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E108" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>45247.69616898148</v>
+        <v>46139.52431712963</v>
       </c>
       <c r="B109" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C109" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D109" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E109" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>45247.86167824074</v>
+        <v>46139.69873842593</v>
       </c>
       <c r="B110" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C110" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="D110" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E110" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4493,30 +4493,30 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45248.03383101852</v>
+        <v>46140.02158564814</v>
       </c>
       <c r="B111" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C111" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D111" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E111" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4525,72 +4525,72 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>45248.22371527777</v>
+        <v>46140.19370370371</v>
       </c>
       <c r="B112" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C112" t="n">
+        <v>74</v>
+      </c>
+      <c r="D112" t="n">
         <v>33</v>
       </c>
-      <c r="D112" t="n">
-        <v>32</v>
-      </c>
       <c r="E112" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>45248.36859953704</v>
+        <v>46140.35989583333</v>
       </c>
       <c r="B113" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C113" t="n">
+        <v>72</v>
+      </c>
+      <c r="D113" t="n">
         <v>35</v>
       </c>
-      <c r="D113" t="n">
-        <v>31</v>
-      </c>
       <c r="E113" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -4604,30 +4604,30 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>45248.53355324074</v>
+        <v>46140.52547453704</v>
       </c>
       <c r="B114" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C114" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D114" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E114" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4636,113 +4636,113 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>45248.69059027778</v>
+        <v>46140.69204861111</v>
       </c>
       <c r="B115" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C115" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D115" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E115" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>45248.85614583334</v>
+        <v>46140.85797453704</v>
       </c>
       <c r="B116" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C116" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D116" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E116" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>45249.02422453704</v>
+        <v>46141.19405092593</v>
       </c>
       <c r="B117" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C117" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D117" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E117" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4752,182 +4752,182 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>45249.20056712963</v>
+        <v>46141.37282407407</v>
       </c>
       <c r="B118" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C118" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D118" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E118" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>45249.36881944445</v>
+        <v>46141.52434027778</v>
       </c>
       <c r="B119" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C119" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D119" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E119" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>45249.54421296297</v>
+        <v>46141.69369212963</v>
       </c>
       <c r="B120" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C120" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D120" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E120" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>45249.7016087963</v>
+        <v>46141.85452546296</v>
       </c>
       <c r="B121" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C121" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D121" t="n">
         <v>33</v>
       </c>
       <c r="E121" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>45249.85693287037</v>
+        <v>46142.09556712963</v>
       </c>
       <c r="B122" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C122" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D122" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E122" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4937,30 +4937,30 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>45250.02412037037</v>
+        <v>46142.22015046296</v>
       </c>
       <c r="B123" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C123" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D123" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E123" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -4974,30 +4974,30 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>45250.20712962963</v>
+        <v>46142.35427083333</v>
       </c>
       <c r="B124" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C124" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D124" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E124" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5011,67 +5011,67 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>45250.52333333333</v>
+        <v>46142.52810185185</v>
       </c>
       <c r="B125" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C125" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D125" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E125" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>45251.205625</v>
+        <v>46142.70089120371</v>
       </c>
       <c r="B126" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C126" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D126" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E126" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5080,72 +5080,72 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>45251.36144675926</v>
+        <v>46142.85965277778</v>
       </c>
       <c r="B127" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C127" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D127" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E127" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>45251.52275462963</v>
+        <v>46143.02594907407</v>
       </c>
       <c r="B128" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C128" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D128" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E128" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5154,76 +5154,76 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>45251.89483796297</v>
+        <v>46143.35506944444</v>
       </c>
       <c r="B129" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C129" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D129" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E129" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>45252.02288194445</v>
+        <v>46143.52101851852</v>
       </c>
       <c r="B130" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C130" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="D130" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E130" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5233,71 +5233,71 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>45252.21390046296</v>
+        <v>46143.69318287037</v>
       </c>
       <c r="B131" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C131" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D131" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E131" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>45252.36752314815</v>
+        <v>46143.86835648148</v>
       </c>
       <c r="B132" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C132" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="D132" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E132" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5307,34 +5307,34 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>45252.52262731481</v>
+        <v>46144.02177083334</v>
       </c>
       <c r="B133" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C133" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="D133" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E133" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5344,34 +5344,34 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>45252.68975694444</v>
+        <v>46144.18803240741</v>
       </c>
       <c r="B134" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C134" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="D134" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E134" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5381,30 +5381,30 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45253.03240740741</v>
+        <v>46144.35827546296</v>
       </c>
       <c r="B135" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C135" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D135" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E135" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -5423,25 +5423,25 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>45253.19027777778</v>
+        <v>46144.52101851852</v>
       </c>
       <c r="B136" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C136" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D136" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E136" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -5450,220 +5450,220 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>45253.35717592593</v>
+        <v>46144.69450231481</v>
       </c>
       <c r="B137" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C137" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D137" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E137" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>45253.52355324074</v>
+        <v>46144.85748842593</v>
       </c>
       <c r="B138" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C138" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D138" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E138" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>45253.69</v>
+        <v>46145.06841435185</v>
       </c>
       <c r="B139" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C139" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D139" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E139" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>45253.86288194444</v>
+        <v>46145.20671296296</v>
       </c>
       <c r="B140" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C140" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="D140" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E140" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>45254.03780092593</v>
+        <v>46145.35491898148</v>
       </c>
       <c r="B141" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C141" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D141" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E141" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>45254.19773148148</v>
+        <v>46145.52814814815</v>
       </c>
       <c r="B142" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C142" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D142" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E142" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5672,72 +5672,72 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>45254.35577546297</v>
+        <v>46145.85527777778</v>
       </c>
       <c r="B143" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C143" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D143" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E143" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>45254.52780092593</v>
+        <v>46146.09436342592</v>
       </c>
       <c r="B144" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C144" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D144" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E144" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5746,1421 +5746,52 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>45254.68921296296</v>
+        <v>46146.21984953704</v>
       </c>
       <c r="B145" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C145" t="n">
+        <v>72</v>
+      </c>
+      <c r="D145" t="n">
         <v>37</v>
       </c>
-      <c r="D145" t="n">
-        <v>31</v>
-      </c>
       <c r="E145" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>45254.86484953704</v>
-      </c>
-      <c r="B146" t="n">
-        <v>32</v>
-      </c>
-      <c r="C146" t="n">
-        <v>37</v>
-      </c>
-      <c r="D146" t="n">
-        <v>31</v>
-      </c>
-      <c r="E146" t="n">
-        <v>51</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>45255.20597222223</v>
-      </c>
-      <c r="B147" t="n">
-        <v>30</v>
-      </c>
-      <c r="C147" t="n">
-        <v>36</v>
-      </c>
-      <c r="D147" t="n">
-        <v>30</v>
-      </c>
-      <c r="E147" t="n">
-        <v>53</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>45255.35901620371</v>
-      </c>
-      <c r="B148" t="n">
-        <v>30</v>
-      </c>
-      <c r="C148" t="n">
-        <v>36</v>
-      </c>
-      <c r="D148" t="n">
-        <v>30</v>
-      </c>
-      <c r="E148" t="n">
-        <v>53</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>45255.52479166666</v>
-      </c>
-      <c r="B149" t="n">
-        <v>32</v>
-      </c>
-      <c r="C149" t="n">
-        <v>36</v>
-      </c>
-      <c r="D149" t="n">
-        <v>31</v>
-      </c>
-      <c r="E149" t="n">
-        <v>52</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>45255.68916666666</v>
-      </c>
-      <c r="B150" t="n">
-        <v>33</v>
-      </c>
-      <c r="C150" t="n">
-        <v>38</v>
-      </c>
-      <c r="D150" t="n">
-        <v>31</v>
-      </c>
-      <c r="E150" t="n">
-        <v>51</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>45255.85908564815</v>
-      </c>
-      <c r="B151" t="n">
-        <v>30</v>
-      </c>
-      <c r="C151" t="n">
-        <v>38</v>
-      </c>
-      <c r="D151" t="n">
-        <v>32</v>
-      </c>
-      <c r="E151" t="n">
-        <v>52</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>45256.02885416667</v>
-      </c>
-      <c r="B152" t="n">
-        <v>30</v>
-      </c>
-      <c r="C152" t="n">
-        <v>38</v>
-      </c>
-      <c r="D152" t="n">
-        <v>32</v>
-      </c>
-      <c r="E152" t="n">
-        <v>52</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>45256.35721064815</v>
-      </c>
-      <c r="B153" t="n">
-        <v>29</v>
-      </c>
-      <c r="C153" t="n">
-        <v>38</v>
-      </c>
-      <c r="D153" t="n">
-        <v>31</v>
-      </c>
-      <c r="E153" t="n">
-        <v>52</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>45256.52245370371</v>
-      </c>
-      <c r="B154" t="n">
-        <v>32</v>
-      </c>
-      <c r="C154" t="n">
-        <v>38</v>
-      </c>
-      <c r="D154" t="n">
-        <v>30</v>
-      </c>
-      <c r="E154" t="n">
-        <v>52</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>45256.69059027778</v>
-      </c>
-      <c r="B155" t="n">
-        <v>33</v>
-      </c>
-      <c r="C155" t="n">
-        <v>38</v>
-      </c>
-      <c r="D155" t="n">
-        <v>31</v>
-      </c>
-      <c r="E155" t="n">
-        <v>53</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>45256.85734953704</v>
-      </c>
-      <c r="B156" t="n">
-        <v>31</v>
-      </c>
-      <c r="C156" t="n">
-        <v>37</v>
-      </c>
-      <c r="D156" t="n">
-        <v>30</v>
-      </c>
-      <c r="E156" t="n">
-        <v>52</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>45257.19155092593</v>
-      </c>
-      <c r="B157" t="n">
-        <v>27</v>
-      </c>
-      <c r="C157" t="n">
-        <v>33</v>
-      </c>
-      <c r="D157" t="n">
-        <v>29</v>
-      </c>
-      <c r="E157" t="n">
-        <v>51</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>45257.35650462963</v>
-      </c>
-      <c r="B158" t="n">
-        <v>32</v>
-      </c>
-      <c r="C158" t="n">
-        <v>37</v>
-      </c>
-      <c r="D158" t="n">
-        <v>29</v>
-      </c>
-      <c r="E158" t="n">
-        <v>82</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>45257.53321759259</v>
-      </c>
-      <c r="B159" t="n">
-        <v>32</v>
-      </c>
-      <c r="C159" t="n">
-        <v>37</v>
-      </c>
-      <c r="D159" t="n">
-        <v>29</v>
-      </c>
-      <c r="E159" t="n">
-        <v>53</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>45257.70081018518</v>
-      </c>
-      <c r="B160" t="n">
-        <v>33</v>
-      </c>
-      <c r="C160" t="n">
-        <v>40</v>
-      </c>
-      <c r="D160" t="n">
-        <v>31</v>
-      </c>
-      <c r="E160" t="n">
-        <v>52</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>45257.86366898148</v>
-      </c>
-      <c r="B161" t="n">
-        <v>32</v>
-      </c>
-      <c r="C161" t="n">
-        <v>38</v>
-      </c>
-      <c r="D161" t="n">
-        <v>29</v>
-      </c>
-      <c r="E161" t="n">
-        <v>51</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>45258.37204861111</v>
-      </c>
-      <c r="B162" t="n">
-        <v>30</v>
-      </c>
-      <c r="C162" t="n">
-        <v>37</v>
-      </c>
-      <c r="D162" t="n">
-        <v>30</v>
-      </c>
-      <c r="E162" t="n">
-        <v>50</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>45258.52905092593</v>
-      </c>
-      <c r="B163" t="n">
-        <v>30</v>
-      </c>
-      <c r="C163" t="n">
-        <v>37</v>
-      </c>
-      <c r="D163" t="n">
-        <v>30</v>
-      </c>
-      <c r="E163" t="n">
-        <v>50</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="n">
-        <v>45258.6908912037</v>
-      </c>
-      <c r="B164" t="n">
-        <v>32</v>
-      </c>
-      <c r="C164" t="n">
-        <v>41</v>
-      </c>
-      <c r="D164" t="n">
-        <v>30</v>
-      </c>
-      <c r="E164" t="n">
-        <v>51</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="1" t="n">
-        <v>45258.85935185185</v>
-      </c>
-      <c r="B165" t="n">
-        <v>32</v>
-      </c>
-      <c r="C165" t="n">
-        <v>41</v>
-      </c>
-      <c r="D165" t="n">
-        <v>30</v>
-      </c>
-      <c r="E165" t="n">
-        <v>51</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="n">
-        <v>45259.35609953704</v>
-      </c>
-      <c r="B166" t="n">
-        <v>33</v>
-      </c>
-      <c r="C166" t="n">
-        <v>37</v>
-      </c>
-      <c r="D166" t="n">
-        <v>31</v>
-      </c>
-      <c r="E166" t="n">
-        <v>53</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="n">
-        <v>45259.52444444445</v>
-      </c>
-      <c r="B167" t="n">
-        <v>33</v>
-      </c>
-      <c r="C167" t="n">
-        <v>38</v>
-      </c>
-      <c r="D167" t="n">
-        <v>31</v>
-      </c>
-      <c r="E167" t="n">
-        <v>53</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="n">
-        <v>45259.68962962963</v>
-      </c>
-      <c r="B168" t="n">
-        <v>32</v>
-      </c>
-      <c r="C168" t="n">
-        <v>38</v>
-      </c>
-      <c r="D168" t="n">
-        <v>30</v>
-      </c>
-      <c r="E168" t="n">
-        <v>51</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="1" t="n">
-        <v>45259.87177083334</v>
-      </c>
-      <c r="B169" t="n">
-        <v>31</v>
-      </c>
-      <c r="C169" t="n">
-        <v>38</v>
-      </c>
-      <c r="D169" t="n">
-        <v>30</v>
-      </c>
-      <c r="E169" t="n">
-        <v>52</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="n">
-        <v>45260.36225694444</v>
-      </c>
-      <c r="B170" t="n">
-        <v>33</v>
-      </c>
-      <c r="C170" t="n">
-        <v>38</v>
-      </c>
-      <c r="D170" t="n">
-        <v>31</v>
-      </c>
-      <c r="E170" t="n">
-        <v>53</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="n">
-        <v>45260.52806712963</v>
-      </c>
-      <c r="B171" t="n">
-        <v>32</v>
-      </c>
-      <c r="C171" t="n">
-        <v>38</v>
-      </c>
-      <c r="D171" t="n">
-        <v>31</v>
-      </c>
-      <c r="E171" t="n">
-        <v>52</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="n">
-        <v>45260.6908912037</v>
-      </c>
-      <c r="B172" t="n">
-        <v>35</v>
-      </c>
-      <c r="C172" t="n">
-        <v>39</v>
-      </c>
-      <c r="D172" t="n">
-        <v>30</v>
-      </c>
-      <c r="E172" t="n">
-        <v>51</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="n">
-        <v>45260.85832175926</v>
-      </c>
-      <c r="B173" t="n">
-        <v>33</v>
-      </c>
-      <c r="C173" t="n">
-        <v>37</v>
-      </c>
-      <c r="D173" t="n">
-        <v>30</v>
-      </c>
-      <c r="E173" t="n">
-        <v>50</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="n">
-        <v>45261.02476851852</v>
-      </c>
-      <c r="B174" t="n">
-        <v>33</v>
-      </c>
-      <c r="C174" t="n">
-        <v>37</v>
-      </c>
-      <c r="D174" t="n">
-        <v>30</v>
-      </c>
-      <c r="E174" t="n">
-        <v>50</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="n">
-        <v>45261.20547453704</v>
-      </c>
-      <c r="B175" t="n">
-        <v>34</v>
-      </c>
-      <c r="C175" t="n">
-        <v>35</v>
-      </c>
-      <c r="D175" t="n">
-        <v>29</v>
-      </c>
-      <c r="E175" t="n">
-        <v>51</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="1" t="n">
-        <v>45261.52430555555</v>
-      </c>
-      <c r="B176" t="n">
-        <v>28</v>
-      </c>
-      <c r="C176" t="n">
-        <v>35</v>
-      </c>
-      <c r="D176" t="n">
-        <v>33</v>
-      </c>
-      <c r="E176" t="n">
-        <v>62</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="n">
-        <v>45261.704375</v>
-      </c>
-      <c r="B177" t="n">
-        <v>33</v>
-      </c>
-      <c r="C177" t="n">
-        <v>37</v>
-      </c>
-      <c r="D177" t="n">
-        <v>32</v>
-      </c>
-      <c r="E177" t="n">
-        <v>61</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="n">
-        <v>45261.86386574074</v>
-      </c>
-      <c r="B178" t="n">
-        <v>31</v>
-      </c>
-      <c r="C178" t="n">
-        <v>37</v>
-      </c>
-      <c r="D178" t="n">
-        <v>30</v>
-      </c>
-      <c r="E178" t="n">
-        <v>58</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="n">
-        <v>45262.03394675926</v>
-      </c>
-      <c r="B179" t="n">
-        <v>35</v>
-      </c>
-      <c r="C179" t="n">
-        <v>35</v>
-      </c>
-      <c r="D179" t="n">
-        <v>31</v>
-      </c>
-      <c r="E179" t="n">
-        <v>56</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="1" t="n">
-        <v>45262.20064814815</v>
-      </c>
-      <c r="B180" t="n">
-        <v>35</v>
-      </c>
-      <c r="C180" t="n">
-        <v>36</v>
-      </c>
-      <c r="D180" t="n">
-        <v>30</v>
-      </c>
-      <c r="E180" t="n">
-        <v>58</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="1" t="n">
-        <v>45262.3559837963</v>
-      </c>
-      <c r="B181" t="n">
-        <v>35</v>
-      </c>
-      <c r="C181" t="n">
-        <v>36</v>
-      </c>
-      <c r="D181" t="n">
-        <v>30</v>
-      </c>
-      <c r="E181" t="n">
-        <v>58</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="1" t="n">
-        <v>45262.53416666666</v>
-      </c>
-      <c r="B182" t="n">
-        <v>33</v>
-      </c>
-      <c r="C182" t="n">
-        <v>38</v>
-      </c>
-      <c r="D182" t="n">
-        <v>32</v>
-      </c>
-      <c r="E182" t="n">
-        <v>60</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
@@ -7225,309 +5856,309 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AssetID_12208</t>
+          <t>AssetID_9368</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6058165127988354</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.130024781901016</v>
+        <v>0.2225398660724854</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.4552825457439341</v>
       </c>
       <c r="E2" t="n">
-        <v>1.565586271009392</v>
+        <v>1.043349350237618</v>
       </c>
       <c r="F2" t="n">
-        <v>0.150466937475308</v>
+        <v>0.1492367802267725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8029082563994177</v>
+        <v>0.727641272871967</v>
       </c>
       <c r="H2" t="n">
-        <v>0.682097109985358</v>
+        <v>0.6190504321484442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AssetID_9368</t>
+          <t>AssetID_9344</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.2805277825879355</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1696992519562923</v>
+        <v>0.1387230846230699</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4865463348248384</v>
+        <v>0.9184618420202899</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8520073686260012</v>
+        <v>2.076674653340274</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1505410724323968</v>
+        <v>0.1276790845347636</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7432731674124192</v>
+        <v>0.5994948123041127</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6313800276799293</v>
+        <v>0.5229518634857837</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AssetID_9358</t>
+          <t>AssetID_9343</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9773531520106988</v>
+        <v>0.968373196798675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1674198523325851</v>
+        <v>0.2188554196300581</v>
       </c>
       <c r="D4" t="n">
-        <v>0.455599822414374</v>
+        <v>0.2117177355958799</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8089990509213846</v>
+        <v>0.499970828583634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.16333836063694</v>
+        <v>0.1258606478995332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7164764872125364</v>
+        <v>0.5900454661972774</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5994483923563272</v>
+        <v>0.5157819615315059</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AssetID_9343</t>
+          <t>AssetID_9360</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6808068344526133</v>
+        <v>0.2827459172424124</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1375725391447638</v>
+        <v>0.1389814919709288</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4313124997360688</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.775245428668627</v>
+        <v>2.258581406267644</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0848718712234858</v>
+        <v>0.2107179053512696</v>
       </c>
       <c r="G5" t="n">
-        <v>0.556059667094341</v>
+        <v>0.6413729586212062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5088658426361357</v>
+        <v>0.5062241922315992</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AssetID_9361</t>
+          <t>AssetID_9359</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9697624681181818</v>
+        <v>0.7321617049641899</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1666558518846438</v>
+        <v>0.1913373494283394</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01486243257576336</v>
+        <v>0.4552433150533241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1964785369757568</v>
+        <v>1.043261828913605</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07540671194741769</v>
+        <v>0.1732367886090501</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4923124503469726</v>
+        <v>0.593702510008757</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4551887872155311</v>
+        <v>0.4908513937857075</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AssetID_9369</t>
+          <t>AssetID_9358</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9532421455488864</v>
+        <v>0.6172738940904606</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1649930855223773</v>
+        <v>0.1779531960139901</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1823427050110301</v>
+        <v>0.538046414499065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4292364216321232</v>
+        <v>1.227990590584245</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2075097448318802</v>
+        <v>0.1592283532526883</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5677924252799582</v>
+        <v>0.5776601542947628</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4499699639926397</v>
+        <v>0.4856802791867139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AssetID_9359</t>
+          <t>AssetID_9357</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7364409006237482</v>
+        <v>0.4262056697373911</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1431720940830799</v>
+        <v>0.1556942078071432</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.5544879383085241</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1758232781988186</v>
+        <v>1.264670646688786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1735759459548614</v>
+        <v>0.2035845375482461</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3682204503118741</v>
+        <v>0.4903468040229576</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3043062373290655</v>
+        <v>0.3905197766876833</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AssetID_9360</t>
+          <t>AssetID_9361</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5799320619150637</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1274195183503352</v>
+        <v>0.1060422732246284</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07568764323385919</v>
+        <v>0.9416868986872772</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2810111637782857</v>
+        <v>2.128488365466284</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1433155720122158</v>
+        <v>0.17148967768238</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3278098525744615</v>
+        <v>0.4708434493436386</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2808295960415124</v>
+        <v>0.390098657976838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AssetID_9370</t>
+          <t>AssetID_9369</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3779757544698107</v>
+        <v>0.1438201510859209</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1070926661802903</v>
+        <v>0.1227969746291533</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04400017499895783</v>
+        <v>0.3122848354277141</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2369730930895592</v>
+        <v>0.7243300124921525</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2247596980260419</v>
+        <v>0.12365551147697</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2109879647343843</v>
+        <v>0.2280524932568175</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1635663734935549</v>
+        <v>0.1998525455595475</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AssetID_9408</t>
+          <t>AssetID_9370</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3302979288678056</v>
+        <v>0.2874929591557742</v>
       </c>
       <c r="C11" t="n">
-        <v>0.102293904878597</v>
+        <v>0.1395345109269834</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007550253037808591</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1863163404571206</v>
+        <v>0.02764122519762795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05855527959537817</v>
+        <v>0.06711187686538431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1689240909528071</v>
+        <v>0.1437464795778871</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1590326935766704</v>
+        <v>0.1340993835406235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AssetID_9344</t>
+          <t>AssetID_9408</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.01737157963859497</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06904950039775201</v>
+        <v>0.1080660204364896</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09587726622969953</v>
+        <v>0.1029679402809263</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3090699546567019</v>
+        <v>0.2573565405323642</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09786923268525574</v>
+        <v>0.08280488092551568</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04793863311484976</v>
+        <v>0.06016975995976064</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04324691587591942</v>
+        <v>0.0551874101509758</v>
       </c>
     </row>
   </sheetData>
@@ -7582,7 +6213,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>AssetID_12208</t>
+          <t>AssetID_9357</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -7611,34 +6242,34 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2509287841195013</v>
+        <v>-0.4136578716220328</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1298801868493328</v>
+        <v>0.177486512111706</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1617124050268189</v>
+        <v>0.07517778285859036</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1613325598449466</v>
+        <v>0.0427798187178567</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1231666180856991</v>
+        <v>0.1130970460004365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1438630280998802</v>
+        <v>-0.1673845364924884</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2157108814343903</v>
+        <v>-0.2530682169462686</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2122993332488231</v>
+        <v>-0.3766067117376183</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.031272810442625</v>
+        <v>-0.05345671484498481</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2440319161738334</v>
+        <v>0.1068167488079185</v>
       </c>
     </row>
     <row r="3">
@@ -7648,37 +6279,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2509287841195015</v>
+        <v>-0.413657871622033</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03923843191442124</v>
+        <v>0.08772588658859869</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2240663531564866</v>
+        <v>-0.001037140722880026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002018460983940394</v>
+        <v>0.2162417779053431</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2098210782697555</v>
+        <v>-0.3837159886804418</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03281458334054654</v>
+        <v>0.1798399291210796</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2335832441205688</v>
+        <v>-0.2468719311611856</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3301711975153326</v>
+        <v>0.2989656483713755</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.01597315291045948</v>
+        <v>0.02303140054901041</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.09310565449978633</v>
+        <v>0.06228591956144634</v>
       </c>
     </row>
     <row r="4">
@@ -7688,37 +6319,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1298801868493328</v>
+        <v>0.1774865121117059</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03923843191442115</v>
+        <v>0.08772588658859867</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.435600817015686</v>
+        <v>0.09945659438796417</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04319348813835848</v>
+        <v>-0.3159631615273557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04302100035990616</v>
+        <v>-0.03508442873228342</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04503528719018562</v>
+        <v>0.08534553438487304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08967427727361488</v>
+        <v>0.1049788466199092</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.08863192712830073</v>
+        <v>-0.1885323921636738</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2463750439638123</v>
+        <v>0.2498420195039772</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1135447236697334</v>
+        <v>-0.04539954368894749</v>
       </c>
     </row>
     <row r="5">
@@ -7728,37 +6359,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1617124050268189</v>
+        <v>0.07517778285859042</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2240663531564866</v>
+        <v>-0.001037140722880053</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.435600817015686</v>
+        <v>0.09945659438796417</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3622935322386172</v>
+        <v>0.1851494496246698</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0157279253066343</v>
+        <v>0.02246240364054738</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1445567105924209</v>
+        <v>0.05703821064574031</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1167793283440166</v>
+        <v>-0.2317324865774227</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.03211205415594846</v>
+        <v>-0.1321377736750483</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1031104547213856</v>
+        <v>-0.1798097516595015</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07059893828842329</v>
+        <v>0.07642113845391979</v>
       </c>
     </row>
     <row r="6">
@@ -7768,37 +6399,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1613325598449465</v>
+        <v>0.04277981871785679</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002018460983940248</v>
+        <v>0.216241777905343</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04319348813835867</v>
+        <v>-0.3159631615273557</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3622935322386173</v>
+        <v>0.1851494496246698</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5534651901577492</v>
+        <v>-0.2867339183971511</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3069636908849557</v>
+        <v>-0.3978122002897308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1126762309205156</v>
+        <v>0.1463777517906021</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.09515615083800361</v>
+        <v>0.1061567520416884</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05680059682039574</v>
+        <v>0.2798444098899119</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0030926187354402</v>
+        <v>-0.2483394205405445</v>
       </c>
     </row>
     <row r="7">
@@ -7808,37 +6439,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1231666180856991</v>
+        <v>0.1130970460004364</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2098210782697553</v>
+        <v>-0.3837159886804416</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04302100035990611</v>
+        <v>-0.0350844287322834</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01572792530663446</v>
+        <v>0.02246240364054738</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5534651901577494</v>
+        <v>-0.2867339183971512</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1514167717823364</v>
+        <v>-0.03106116462096556</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2571285401665077</v>
+        <v>-0.1209176226454808</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1158058459353949</v>
+        <v>0.1134347001148509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04636341810411252</v>
+        <v>-0.05093977925214002</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1340144670556769</v>
+        <v>0.07052269420723579</v>
       </c>
     </row>
     <row r="8">
@@ -7848,77 +6479,77 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1438630280998801</v>
+        <v>-0.1673845364924884</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.03281458334054635</v>
+        <v>0.1798399291210796</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04503528719018574</v>
+        <v>0.08534553438487306</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1445567105924208</v>
+        <v>0.05703821064574029</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3069636908849561</v>
+        <v>-0.3978122002897307</v>
       </c>
       <c r="G8" t="n">
-        <v>0.151416771782336</v>
+        <v>-0.03106116462096559</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01773880896376692</v>
+        <v>0.1130438241067888</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1324350734978512</v>
+        <v>0.1591796894719563</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.05467869375134003</v>
+        <v>0.0657037912482191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04142401369961966</v>
+        <v>0.1389362288879923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AssetID_12208</t>
+          <t>AssetID_9357</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.2157108814343904</v>
+        <v>-0.2530682169462687</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2335832441205689</v>
+        <v>-0.2468719311611856</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08967427727361504</v>
+        <v>0.104978846619909</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1167793283440167</v>
+        <v>-0.2317324865774224</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1126762309205158</v>
+        <v>0.1463777517906021</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2571285401665076</v>
+        <v>-0.1209176226454809</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.01773880896376717</v>
+        <v>0.1130438241067887</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1246440559575958</v>
+        <v>0.2190381975553199</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0632489712804406</v>
+        <v>0.1030131427409759</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06906348054874208</v>
+        <v>0.01790005792747899</v>
       </c>
     </row>
     <row r="10">
@@ -7928,37 +6559,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2122993332488232</v>
+        <v>-0.3766067117376184</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3301711975153325</v>
+        <v>0.2989656483713754</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08863192712830067</v>
+        <v>-0.188532392163674</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03211205415594844</v>
+        <v>-0.1321377736750482</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09515615083800358</v>
+        <v>0.1061567520416884</v>
       </c>
       <c r="G10" t="n">
-        <v>0.115805845935395</v>
+        <v>0.1134347001148509</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1324350734978512</v>
+        <v>0.1591796894719563</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1246440559575957</v>
+        <v>0.2190381975553199</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03153918951931048</v>
+        <v>-0.3310268577108078</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2129305636510768</v>
+        <v>-0.2634754734582423</v>
       </c>
     </row>
     <row r="11">
@@ -7968,37 +6599,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.03127281044262496</v>
+        <v>-0.05345671484498486</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.01597315291045953</v>
+        <v>0.02303140054901042</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2463750439638122</v>
+        <v>0.2498420195039773</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1031104547213856</v>
+        <v>-0.1798097516595016</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05680059682039573</v>
+        <v>0.2798444098899119</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04636341810411253</v>
+        <v>-0.05093977925214009</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.05467869375134006</v>
+        <v>0.0657037912482191</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0632489712804406</v>
+        <v>0.103013142740976</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03153918951931049</v>
+        <v>-0.3310268577108078</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.04113267246363854</v>
+        <v>-0.05056297883116995</v>
       </c>
     </row>
     <row r="12">
@@ -8008,34 +6639,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2440319161738334</v>
+        <v>0.1068167488079185</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.09310565449978625</v>
+        <v>0.06228591956144632</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1135447236697333</v>
+        <v>-0.04539954368894746</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07059893828842326</v>
+        <v>0.07642113845391973</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.003092618735440228</v>
+        <v>-0.2483394205405445</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1340144670556769</v>
+        <v>0.07052269420723578</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04142401369961969</v>
+        <v>0.1389362288879923</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06906348054874209</v>
+        <v>0.01790005792747899</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2129305636510768</v>
+        <v>-0.2634754734582423</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.04113267246363854</v>
+        <v>-0.05056297883116995</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>

--- a/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output1.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fault_Status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RCA_Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Delta_Correlation_Matrix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fault_Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RCA_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delta_Correlation_Matrix" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +22,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -419,58 +431,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9358</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9359</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9360</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9361</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Status_AssetID_9358</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status_AssetID_9359</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status_AssetID_9360</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Status_AssetID_9361</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46116.3550925926</v>
       </c>
       <c r="B2" t="n">
@@ -507,7 +519,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46116.52167824074</v>
       </c>
       <c r="B3" t="n">
@@ -544,7 +556,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46116.69474537037</v>
       </c>
       <c r="B4" t="n">
@@ -581,7 +593,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46116.85944444445</v>
       </c>
       <c r="B5" t="n">
@@ -618,7 +630,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46117.03664351852</v>
       </c>
       <c r="B6" t="n">
@@ -655,7 +667,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46117.24065972222</v>
       </c>
       <c r="B7" t="n">
@@ -692,7 +704,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46117.36049768519</v>
       </c>
       <c r="B8" t="n">
@@ -729,7 +741,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46117.52633101852</v>
       </c>
       <c r="B9" t="n">
@@ -766,7 +778,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46117.69008101852</v>
       </c>
       <c r="B10" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46117.87108796297</v>
       </c>
       <c r="B11" t="n">
@@ -840,7 +852,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46118.0265625</v>
       </c>
       <c r="B12" t="n">
@@ -877,7 +889,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46118.19368055555</v>
       </c>
       <c r="B13" t="n">
@@ -914,7 +926,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46118.36050925926</v>
       </c>
       <c r="B14" t="n">
@@ -951,7 +963,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46118.52253472222</v>
       </c>
       <c r="B15" t="n">
@@ -988,7 +1000,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46118.68907407407</v>
       </c>
       <c r="B16" t="n">
@@ -1025,7 +1037,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46118.8552662037</v>
       </c>
       <c r="B17" t="n">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46119.02732638889</v>
       </c>
       <c r="B18" t="n">
@@ -1099,7 +1111,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46120.18833333333</v>
       </c>
       <c r="B19" t="n">
@@ -1136,7 +1148,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46120.52369212963</v>
       </c>
       <c r="B20" t="n">
@@ -1173,7 +1185,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46120.69190972222</v>
       </c>
       <c r="B21" t="n">
@@ -1210,7 +1222,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46120.85443287037</v>
       </c>
       <c r="B22" t="n">
@@ -1247,7 +1259,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46124.39263888889</v>
       </c>
       <c r="B23" t="n">
@@ -1284,7 +1296,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46124.52407407408</v>
       </c>
       <c r="B24" t="n">
@@ -1321,7 +1333,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46124.69166666667</v>
       </c>
       <c r="B25" t="n">
@@ -1358,7 +1370,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46124.85614583334</v>
       </c>
       <c r="B26" t="n">
@@ -1395,7 +1407,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46125.07673611111</v>
       </c>
       <c r="B27" t="n">
@@ -1432,7 +1444,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46125.18878472222</v>
       </c>
       <c r="B28" t="n">
@@ -1469,29 +1481,29 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46125.37304398148</v>
+      <c r="A29" s="2" t="n">
+        <v>46125.85716435185</v>
       </c>
       <c r="B29" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D29" t="n">
         <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1501,66 +1513,66 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46125.52486111111</v>
+      <c r="A30" s="2" t="n">
+        <v>46126.03134259259</v>
       </c>
       <c r="B30" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C30" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D30" t="n">
         <v>37</v>
       </c>
       <c r="E30" t="n">
+        <v>71</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46126.21274305556</v>
+      </c>
+      <c r="B31" t="n">
+        <v>53</v>
+      </c>
+      <c r="C31" t="n">
         <v>75</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46125.69287037037</v>
-      </c>
-      <c r="B31" t="n">
-        <v>49</v>
-      </c>
-      <c r="C31" t="n">
-        <v>73</v>
-      </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E31" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1570,76 +1582,76 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46125.85716435185</v>
+      <c r="A32" s="2" t="n">
+        <v>46126.35861111111</v>
       </c>
       <c r="B32" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D32" t="n">
         <v>37</v>
       </c>
       <c r="E32" t="n">
+        <v>75</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46126.53461805556</v>
+      </c>
+      <c r="B33" t="n">
+        <v>50</v>
+      </c>
+      <c r="C33" t="n">
         <v>71</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46126.03134259259</v>
-      </c>
-      <c r="B33" t="n">
-        <v>54</v>
-      </c>
-      <c r="C33" t="n">
-        <v>77</v>
-      </c>
       <c r="D33" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E33" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1654,57 +1666,57 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46126.21274305556</v>
+      <c r="A34" s="2" t="n">
+        <v>46126.87692129629</v>
       </c>
       <c r="B34" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C34" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46126.35861111111</v>
+      <c r="A35" s="2" t="n">
+        <v>46127.02172453704</v>
       </c>
       <c r="B35" t="n">
         <v>53</v>
       </c>
       <c r="C35" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D35" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1718,30 +1730,30 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46126.53461805556</v>
+      <c r="A36" s="2" t="n">
+        <v>46127.20758101852</v>
       </c>
       <c r="B36" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C36" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D36" t="n">
         <v>36</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1750,7 +1762,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1765,20 +1777,20 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46126.70118055555</v>
+      <c r="A37" s="2" t="n">
+        <v>46127.35572916667</v>
       </c>
       <c r="B37" t="n">
         <v>51</v>
       </c>
       <c r="C37" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1787,32 +1799,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46126.87692129629</v>
+      <c r="A38" s="2" t="n">
+        <v>46127.53050925926</v>
       </c>
       <c r="B38" t="n">
         <v>51</v>
       </c>
       <c r="C38" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38" t="n">
         <v>70</v>
@@ -1824,12 +1836,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1839,17 +1851,17 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46127.02172453704</v>
+      <c r="A39" s="2" t="n">
+        <v>46128.04122685185</v>
       </c>
       <c r="B39" t="n">
         <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
         <v>70</v>
@@ -1866,7 +1878,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1876,24 +1888,24 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46127.20758101852</v>
+      <c r="A40" s="2" t="n">
+        <v>46128.19846064815</v>
       </c>
       <c r="B40" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1908,25 +1920,25 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46127.35572916667</v>
+      <c r="A41" s="2" t="n">
+        <v>46128.3578125</v>
       </c>
       <c r="B41" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D41" t="n">
         <v>36</v>
       </c>
       <c r="E41" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1935,7 +1947,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1950,20 +1962,20 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46127.53050925926</v>
+      <c r="A42" s="2" t="n">
+        <v>46128.69186342593</v>
       </c>
       <c r="B42" t="n">
         <v>51</v>
       </c>
       <c r="C42" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D42" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E42" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1972,12 +1984,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46127.69168981481</v>
+      <c r="A43" s="2" t="n">
+        <v>46128.85454861111</v>
       </c>
       <c r="B43" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" t="n">
         <v>72</v>
@@ -2000,7 +2012,7 @@
         <v>34</v>
       </c>
       <c r="E43" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2019,34 +2031,34 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46127.85546296297</v>
+      <c r="A44" s="2" t="n">
+        <v>46129.08709490741</v>
       </c>
       <c r="B44" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D44" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E44" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2056,103 +2068,103 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46128.04122685185</v>
+      <c r="A45" s="2" t="n">
+        <v>46129.20550925926</v>
       </c>
       <c r="B45" t="n">
+        <v>50</v>
+      </c>
+      <c r="C45" t="n">
+        <v>72</v>
+      </c>
+      <c r="D45" t="n">
+        <v>35</v>
+      </c>
+      <c r="E45" t="n">
+        <v>72</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46129.52703703703</v>
+      </c>
+      <c r="B46" t="n">
+        <v>49</v>
+      </c>
+      <c r="C46" t="n">
+        <v>72</v>
+      </c>
+      <c r="D46" t="n">
+        <v>35</v>
+      </c>
+      <c r="E46" t="n">
+        <v>72</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46129.85914351852</v>
+      </c>
+      <c r="B47" t="n">
         <v>53</v>
-      </c>
-      <c r="C45" t="n">
-        <v>75</v>
-      </c>
-      <c r="D45" t="n">
-        <v>34</v>
-      </c>
-      <c r="E45" t="n">
-        <v>70</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46128.19846064815</v>
-      </c>
-      <c r="B46" t="n">
-        <v>52</v>
-      </c>
-      <c r="C46" t="n">
-        <v>75</v>
-      </c>
-      <c r="D46" t="n">
-        <v>37</v>
-      </c>
-      <c r="E46" t="n">
-        <v>73</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46128.3578125</v>
-      </c>
-      <c r="B47" t="n">
-        <v>50</v>
       </c>
       <c r="C47" t="n">
         <v>72</v>
       </c>
       <c r="D47" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E47" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2162,68 +2174,68 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46128.52149305555</v>
+      <c r="A48" s="2" t="n">
+        <v>46130.09744212963</v>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C48" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D48" t="n">
         <v>34</v>
       </c>
       <c r="E48" t="n">
+        <v>68</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46131.02777777778</v>
+      </c>
+      <c r="B49" t="n">
+        <v>50</v>
+      </c>
+      <c r="C49" t="n">
+        <v>74</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E49" t="n">
         <v>69</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46128.69186342593</v>
-      </c>
-      <c r="B49" t="n">
-        <v>51</v>
-      </c>
-      <c r="C49" t="n">
-        <v>72</v>
-      </c>
-      <c r="D49" t="n">
-        <v>34</v>
-      </c>
-      <c r="E49" t="n">
-        <v>71</v>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Normal (Minor Change)</t>
@@ -2231,174 +2243,174 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46128.85454861111</v>
+      <c r="A50" s="2" t="n">
+        <v>46131.35472222222</v>
       </c>
       <c r="B50" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C50" t="n">
         <v>72</v>
       </c>
       <c r="D50" t="n">
+        <v>35</v>
+      </c>
+      <c r="E50" t="n">
+        <v>72</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46131.52929398148</v>
+      </c>
+      <c r="B51" t="n">
+        <v>52</v>
+      </c>
+      <c r="C51" t="n">
+        <v>72</v>
+      </c>
+      <c r="D51" t="n">
+        <v>35</v>
+      </c>
+      <c r="E51" t="n">
+        <v>72</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46131.68760416667</v>
+      </c>
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="n">
+        <v>71</v>
+      </c>
+      <c r="D52" t="n">
+        <v>33</v>
+      </c>
+      <c r="E52" t="n">
+        <v>68</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46132.02103009259</v>
+      </c>
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" t="n">
+        <v>73</v>
+      </c>
+      <c r="D53" t="n">
         <v>34</v>
       </c>
-      <c r="E50" t="n">
-        <v>71</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46129.08709490741</v>
-      </c>
-      <c r="B51" t="n">
-        <v>51</v>
-      </c>
-      <c r="C51" t="n">
-        <v>71</v>
-      </c>
-      <c r="D51" t="n">
-        <v>34</v>
-      </c>
-      <c r="E51" t="n">
-        <v>71</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46129.20550925926</v>
-      </c>
-      <c r="B52" t="n">
+      <c r="E53" t="n">
+        <v>69</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46132.19717592592</v>
+      </c>
+      <c r="B54" t="n">
         <v>50</v>
-      </c>
-      <c r="C52" t="n">
-        <v>72</v>
-      </c>
-      <c r="D52" t="n">
-        <v>35</v>
-      </c>
-      <c r="E52" t="n">
-        <v>72</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46129.36481481481</v>
-      </c>
-      <c r="B53" t="n">
-        <v>49</v>
-      </c>
-      <c r="C53" t="n">
-        <v>72</v>
-      </c>
-      <c r="D53" t="n">
-        <v>35</v>
-      </c>
-      <c r="E53" t="n">
-        <v>72</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>46129.52703703703</v>
-      </c>
-      <c r="B54" t="n">
-        <v>49</v>
       </c>
       <c r="C54" t="n">
         <v>72</v>
@@ -2407,7 +2419,7 @@
         <v>35</v>
       </c>
       <c r="E54" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2431,29 +2443,29 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46129.69325231481</v>
+      <c r="A55" s="2" t="n">
+        <v>46132.3584375</v>
       </c>
       <c r="B55" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C55" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D55" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E55" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2463,29 +2475,29 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46129.85914351852</v>
+      <c r="A56" s="2" t="n">
+        <v>46132.52159722222</v>
       </c>
       <c r="B56" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C56" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D56" t="n">
         <v>34</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2500,29 +2512,29 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>46130.09744212963</v>
+      <c r="A57" s="2" t="n">
+        <v>46132.69394675926</v>
       </c>
       <c r="B57" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C57" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D57" t="n">
         <v>34</v>
       </c>
       <c r="E57" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2537,29 +2549,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>46130.19385416667</v>
+      <c r="A58" s="2" t="n">
+        <v>46132.86247685185</v>
       </c>
       <c r="B58" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C58" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E58" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2569,7 +2581,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2579,24 +2591,24 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46130.35618055556</v>
+      <c r="A59" s="2" t="n">
+        <v>46133.07111111111</v>
       </c>
       <c r="B59" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C59" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D59" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E59" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2606,7 +2618,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2616,11 +2628,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46130.52403935185</v>
+      <c r="A60" s="2" t="n">
+        <v>46133.19524305555</v>
       </c>
       <c r="B60" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" t="n">
         <v>74</v>
@@ -2629,11 +2641,11 @@
         <v>35</v>
       </c>
       <c r="E60" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2648,29 +2660,29 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46131.02777777778</v>
+      <c r="A61" s="2" t="n">
+        <v>46133.36118055556</v>
       </c>
       <c r="B61" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C61" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D61" t="n">
         <v>35</v>
       </c>
       <c r="E61" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2685,29 +2697,29 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46131.35472222222</v>
+      <c r="A62" s="2" t="n">
+        <v>46133.52528935186</v>
       </c>
       <c r="B62" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C62" t="n">
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E62" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2717,7 +2729,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2727,57 +2739,57 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>46131.52929398148</v>
+      <c r="A63" s="2" t="n">
+        <v>46133.69530092592</v>
       </c>
       <c r="B63" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>46131.68760416667</v>
+      <c r="A64" s="2" t="n">
+        <v>46133.85505787037</v>
       </c>
       <c r="B64" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C64" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D64" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E64" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2786,7 +2798,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2796,13 +2808,13 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>46132.02103009259</v>
+      <c r="A65" s="2" t="n">
+        <v>46134.09811342593</v>
       </c>
       <c r="B65" t="n">
         <v>51</v>
@@ -2814,7 +2826,7 @@
         <v>34</v>
       </c>
       <c r="E65" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2833,34 +2845,34 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>46132.19717592592</v>
+      <c r="A66" s="2" t="n">
+        <v>46134.21712962963</v>
       </c>
       <c r="B66" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C66" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D66" t="n">
         <v>35</v>
       </c>
       <c r="E66" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2875,24 +2887,24 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>46132.3584375</v>
+      <c r="A67" s="2" t="n">
+        <v>46134.85905092592</v>
       </c>
       <c r="B67" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C67" t="n">
         <v>71</v>
       </c>
       <c r="D67" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E67" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2907,103 +2919,103 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>46132.52159722222</v>
+      <c r="A68" s="2" t="n">
+        <v>46135.3603125</v>
       </c>
       <c r="B68" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C68" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D68" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E68" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>46132.69394675926</v>
+      <c r="A69" s="2" t="n">
+        <v>46135.53359953704</v>
       </c>
       <c r="B69" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C69" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D69" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E69" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>46132.86247685185</v>
+      <c r="A70" s="2" t="n">
+        <v>46136.18943287037</v>
       </c>
       <c r="B70" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C70" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D70" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3013,7 +3025,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3023,20 +3035,20 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>46133.07111111111</v>
+      <c r="A71" s="2" t="n">
+        <v>46136.85456018519</v>
       </c>
       <c r="B71" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C71" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D71" t="n">
         <v>34</v>
       </c>
       <c r="E71" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3045,7 +3057,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3060,66 +3072,66 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>46133.19524305555</v>
+      <c r="A72" s="2" t="n">
+        <v>46137.0588425926</v>
       </c>
       <c r="B72" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C72" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D72" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E72" t="n">
+        <v>68</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46137.18950231482</v>
+      </c>
+      <c r="B73" t="n">
+        <v>50</v>
+      </c>
+      <c r="C73" t="n">
         <v>72</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>46133.36118055556</v>
-      </c>
-      <c r="B73" t="n">
-        <v>52</v>
-      </c>
-      <c r="C73" t="n">
-        <v>73</v>
       </c>
       <c r="D73" t="n">
         <v>35</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3129,13 +3141,13 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>46133.52528935186</v>
+      <c r="A74" s="2" t="n">
+        <v>46137.68905092592</v>
       </c>
       <c r="B74" t="n">
         <v>50</v>
@@ -3144,7 +3156,7 @@
         <v>72</v>
       </c>
       <c r="D74" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E74" t="n">
         <v>70</v>
@@ -3171,20 +3183,20 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>46133.69530092592</v>
+      <c r="A75" s="2" t="n">
+        <v>46137.8555787037</v>
       </c>
       <c r="B75" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C75" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D75" t="n">
         <v>34</v>
       </c>
       <c r="E75" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3203,25 +3215,25 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>46133.85505787037</v>
+      <c r="A76" s="2" t="n">
+        <v>46138.08900462963</v>
       </c>
       <c r="B76" t="n">
         <v>51</v>
       </c>
       <c r="C76" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D76" t="n">
         <v>34</v>
       </c>
       <c r="E76" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3240,22 +3252,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>46134.09811342593</v>
+      <c r="A77" s="2" t="n">
+        <v>46138.22342592593</v>
       </c>
       <c r="B77" t="n">
         <v>51</v>
       </c>
       <c r="C77" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D77" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E77" t="n">
         <v>73</v>
@@ -3267,12 +3279,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3282,71 +3294,71 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>46134.21712962963</v>
+      <c r="A78" s="2" t="n">
+        <v>46138.69407407408</v>
       </c>
       <c r="B78" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C78" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D78" t="n">
         <v>35</v>
       </c>
       <c r="E78" t="n">
+        <v>70</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46138.85946759259</v>
+      </c>
+      <c r="B79" t="n">
+        <v>49</v>
+      </c>
+      <c r="C79" t="n">
         <v>72</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>46134.35688657407</v>
-      </c>
-      <c r="B79" t="n">
-        <v>52</v>
-      </c>
-      <c r="C79" t="n">
-        <v>75</v>
-      </c>
       <c r="D79" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E79" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3356,140 +3368,140 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>46134.52453703704</v>
+      <c r="A80" s="2" t="n">
+        <v>46139.04685185185</v>
       </c>
       <c r="B80" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C80" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D80" t="n">
         <v>34</v>
       </c>
       <c r="E80" t="n">
+        <v>69</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46139.20314814815</v>
+      </c>
+      <c r="B81" t="n">
+        <v>50</v>
+      </c>
+      <c r="C81" t="n">
+        <v>73</v>
+      </c>
+      <c r="D81" t="n">
+        <v>35</v>
+      </c>
+      <c r="E81" t="n">
         <v>71</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>46134.72311342593</v>
-      </c>
-      <c r="B81" t="n">
-        <v>49</v>
-      </c>
-      <c r="C81" t="n">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46139.35634259259</v>
+      </c>
+      <c r="B82" t="n">
+        <v>50</v>
+      </c>
+      <c r="C82" t="n">
+        <v>73</v>
+      </c>
+      <c r="D82" t="n">
+        <v>35</v>
+      </c>
+      <c r="E82" t="n">
+        <v>72</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46139.52431712963</v>
+      </c>
+      <c r="B83" t="n">
+        <v>46</v>
+      </c>
+      <c r="C83" t="n">
+        <v>70</v>
+      </c>
+      <c r="D83" t="n">
+        <v>34</v>
+      </c>
+      <c r="E83" t="n">
         <v>71</v>
       </c>
-      <c r="D81" t="n">
-        <v>33</v>
-      </c>
-      <c r="E81" t="n">
-        <v>69</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>46134.85905092592</v>
-      </c>
-      <c r="B82" t="n">
-        <v>49</v>
-      </c>
-      <c r="C82" t="n">
-        <v>71</v>
-      </c>
-      <c r="D82" t="n">
-        <v>33</v>
-      </c>
-      <c r="E82" t="n">
-        <v>69</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>46135.02693287037</v>
-      </c>
-      <c r="B83" t="n">
-        <v>49</v>
-      </c>
-      <c r="C83" t="n">
-        <v>75</v>
-      </c>
-      <c r="D83" t="n">
-        <v>33</v>
-      </c>
-      <c r="E83" t="n">
-        <v>69</v>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3499,25 +3511,25 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>46135.3603125</v>
+      <c r="A84" s="2" t="n">
+        <v>46140.02158564814</v>
       </c>
       <c r="B84" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C84" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D84" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E84" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3526,23 +3538,23 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>46135.53359953704</v>
+      <c r="A85" s="2" t="n">
+        <v>46140.19370370371</v>
       </c>
       <c r="B85" t="n">
         <v>50</v>
@@ -3551,10 +3563,10 @@
         <v>74</v>
       </c>
       <c r="D85" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E85" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3568,24 +3580,24 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>46135.68820601852</v>
+      <c r="A86" s="2" t="n">
+        <v>46140.52547453704</v>
       </c>
       <c r="B86" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C86" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D86" t="n">
         <v>34</v>
@@ -3595,7 +3607,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3615,177 +3627,177 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>46135.86390046297</v>
+      <c r="A87" s="2" t="n">
+        <v>46140.69204861111</v>
       </c>
       <c r="B87" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C87" t="n">
+        <v>72</v>
+      </c>
+      <c r="D87" t="n">
+        <v>34</v>
+      </c>
+      <c r="E87" t="n">
+        <v>68</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46140.85797453704</v>
+      </c>
+      <c r="B88" t="n">
+        <v>49</v>
+      </c>
+      <c r="C88" t="n">
+        <v>71</v>
+      </c>
+      <c r="D88" t="n">
+        <v>34</v>
+      </c>
+      <c r="E88" t="n">
+        <v>69</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46141.85452546296</v>
+      </c>
+      <c r="B89" t="n">
+        <v>49</v>
+      </c>
+      <c r="C89" t="n">
+        <v>70</v>
+      </c>
+      <c r="D89" t="n">
+        <v>33</v>
+      </c>
+      <c r="E89" t="n">
+        <v>70</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46142.09556712963</v>
+      </c>
+      <c r="B90" t="n">
+        <v>49</v>
+      </c>
+      <c r="C90" t="n">
+        <v>70</v>
+      </c>
+      <c r="D90" t="n">
+        <v>33</v>
+      </c>
+      <c r="E90" t="n">
+        <v>70</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Normal (Minor Change)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46142.22015046296</v>
+      </c>
+      <c r="B91" t="n">
+        <v>49</v>
+      </c>
+      <c r="C91" t="n">
         <v>73</v>
-      </c>
-      <c r="D87" t="n">
-        <v>35</v>
-      </c>
-      <c r="E87" t="n">
-        <v>67</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>46136.02126157407</v>
-      </c>
-      <c r="B88" t="n">
-        <v>52</v>
-      </c>
-      <c r="C88" t="n">
-        <v>73</v>
-      </c>
-      <c r="D88" t="n">
-        <v>35</v>
-      </c>
-      <c r="E88" t="n">
-        <v>67</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>46136.18943287037</v>
-      </c>
-      <c r="B89" t="n">
-        <v>52</v>
-      </c>
-      <c r="C89" t="n">
-        <v>75</v>
-      </c>
-      <c r="D89" t="n">
-        <v>36</v>
-      </c>
-      <c r="E89" t="n">
-        <v>69</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>46136.35768518518</v>
-      </c>
-      <c r="B90" t="n">
-        <v>52</v>
-      </c>
-      <c r="C90" t="n">
-        <v>72</v>
-      </c>
-      <c r="D90" t="n">
-        <v>37</v>
-      </c>
-      <c r="E90" t="n">
-        <v>74</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>46136.52224537037</v>
-      </c>
-      <c r="B91" t="n">
-        <v>48</v>
-      </c>
-      <c r="C91" t="n">
-        <v>71</v>
       </c>
       <c r="D91" t="n">
         <v>34</v>
       </c>
       <c r="E91" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3795,19 +3807,19 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>46136.6883912037</v>
+      <c r="A92" s="2" t="n">
+        <v>46142.35427083333</v>
       </c>
       <c r="B92" t="n">
         <v>49</v>
       </c>
       <c r="C92" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D92" t="n">
         <v>34</v>
@@ -3822,7 +3834,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3837,24 +3849,24 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>46136.85456018519</v>
+      <c r="A93" s="2" t="n">
+        <v>46142.52810185185</v>
       </c>
       <c r="B93" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C93" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D93" t="n">
         <v>34</v>
       </c>
       <c r="E93" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3874,14 +3886,14 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>46137.0588425926</v>
+      <c r="A94" s="2" t="n">
+        <v>46142.70089120371</v>
       </c>
       <c r="B94" t="n">
         <v>49</v>
       </c>
       <c r="C94" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D94" t="n">
         <v>34</v>
@@ -3911,20 +3923,20 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>46137.18950231482</v>
+      <c r="A95" s="2" t="n">
+        <v>46142.85965277778</v>
       </c>
       <c r="B95" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C95" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D95" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3933,12 +3945,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -3948,11 +3960,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>46137.36697916667</v>
+      <c r="A96" s="2" t="n">
+        <v>46143.02594907407</v>
       </c>
       <c r="B96" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C96" t="n">
         <v>72</v>
@@ -3961,7 +3973,7 @@
         <v>34</v>
       </c>
       <c r="E96" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3985,14 +3997,14 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>46137.52636574074</v>
+      <c r="A97" s="2" t="n">
+        <v>46143.35506944444</v>
       </c>
       <c r="B97" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C97" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D97" t="n">
         <v>34</v>
@@ -4022,14 +4034,14 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>46137.68905092592</v>
+      <c r="A98" s="2" t="n">
+        <v>46143.52101851852</v>
       </c>
       <c r="B98" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C98" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D98" t="n">
         <v>34</v>
@@ -4039,7 +4051,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4059,20 +4071,20 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>46137.8555787037</v>
+      <c r="A99" s="2" t="n">
+        <v>46143.69318287037</v>
       </c>
       <c r="B99" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C99" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D99" t="n">
         <v>34</v>
       </c>
       <c r="E99" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4081,7 +4093,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4091,25 +4103,25 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>46138.08900462963</v>
+      <c r="A100" s="2" t="n">
+        <v>46143.86835648148</v>
       </c>
       <c r="B100" t="n">
         <v>51</v>
       </c>
       <c r="C100" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D100" t="n">
         <v>34</v>
       </c>
       <c r="E100" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4128,25 +4140,25 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>46138.22342592593</v>
+      <c r="A101" s="2" t="n">
+        <v>46144.02177083334</v>
       </c>
       <c r="B101" t="n">
         <v>51</v>
       </c>
       <c r="C101" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D101" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E101" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4155,60 +4167,60 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>46138.35784722222</v>
+      <c r="A102" s="2" t="n">
+        <v>46144.18803240741</v>
       </c>
       <c r="B102" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C102" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D102" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E102" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>46138.54626157408</v>
+      <c r="A103" s="2" t="n">
+        <v>46144.35827546296</v>
       </c>
       <c r="B103" t="n">
         <v>47</v>
@@ -4217,10 +4229,10 @@
         <v>69</v>
       </c>
       <c r="D103" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E103" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4234,7 +4246,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4244,24 +4256,24 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>46138.69407407408</v>
+      <c r="A104" s="2" t="n">
+        <v>46144.52101851852</v>
       </c>
       <c r="B104" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C104" t="n">
+        <v>70</v>
+      </c>
+      <c r="D104" t="n">
+        <v>34</v>
+      </c>
+      <c r="E104" t="n">
         <v>71</v>
       </c>
-      <c r="D104" t="n">
-        <v>35</v>
-      </c>
-      <c r="E104" t="n">
-        <v>70</v>
-      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4271,7 +4283,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4281,20 +4293,20 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>46138.85946759259</v>
+      <c r="A105" s="2" t="n">
+        <v>46144.69450231481</v>
       </c>
       <c r="B105" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C105" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D105" t="n">
         <v>34</v>
       </c>
       <c r="E105" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4303,7 +4315,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4313,19 +4325,19 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>46139.04685185185</v>
+      <c r="A106" s="2" t="n">
+        <v>46144.85748842593</v>
       </c>
       <c r="B106" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C106" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D106" t="n">
         <v>34</v>
@@ -4335,12 +4347,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4355,20 +4367,20 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>46139.20314814815</v>
+      <c r="A107" s="2" t="n">
+        <v>46145.06841435185</v>
       </c>
       <c r="B107" t="n">
         <v>50</v>
       </c>
       <c r="C107" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D107" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E107" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4377,26 +4389,26 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>46139.35634259259</v>
+      <c r="A108" s="2" t="n">
+        <v>46145.20671296296</v>
       </c>
       <c r="B108" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C108" t="n">
         <v>73</v>
@@ -4409,7 +4421,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Normal (Minor Change)</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4429,57 +4441,57 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>46139.52431712963</v>
+      <c r="A109" s="2" t="n">
+        <v>46145.85527777778</v>
       </c>
       <c r="B109" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C109" t="n">
         <v>70</v>
       </c>
       <c r="D109" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E109" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>46139.69873842593</v>
+      <c r="A110" s="2" t="n">
+        <v>46146.09436342592</v>
       </c>
       <c r="B110" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C110" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D110" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E110" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4493,31 +4505,31 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>46140.02158564814</v>
+      <c r="A111" s="2" t="n">
+        <v>46146.21984953704</v>
       </c>
       <c r="B111" t="n">
         <v>51</v>
       </c>
       <c r="C111" t="n">
+        <v>72</v>
+      </c>
+      <c r="D111" t="n">
+        <v>37</v>
+      </c>
+      <c r="E111" t="n">
         <v>70</v>
       </c>
-      <c r="D111" t="n">
-        <v>34</v>
-      </c>
-      <c r="E111" t="n">
-        <v>68</v>
-      </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>Normal (Minor Change)</t>
@@ -4525,1273 +4537,15 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Action Required</t>
+          <t>Normal (Minor Change)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>46140.19370370371</v>
-      </c>
-      <c r="B112" t="n">
-        <v>50</v>
-      </c>
-      <c r="C112" t="n">
-        <v>74</v>
-      </c>
-      <c r="D112" t="n">
-        <v>33</v>
-      </c>
-      <c r="E112" t="n">
-        <v>69</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>46140.35989583333</v>
-      </c>
-      <c r="B113" t="n">
-        <v>48</v>
-      </c>
-      <c r="C113" t="n">
-        <v>72</v>
-      </c>
-      <c r="D113" t="n">
-        <v>35</v>
-      </c>
-      <c r="E113" t="n">
-        <v>71</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>46140.52547453704</v>
-      </c>
-      <c r="B114" t="n">
-        <v>48</v>
-      </c>
-      <c r="C114" t="n">
-        <v>70</v>
-      </c>
-      <c r="D114" t="n">
-        <v>34</v>
-      </c>
-      <c r="E114" t="n">
-        <v>69</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>46140.69204861111</v>
-      </c>
-      <c r="B115" t="n">
-        <v>48</v>
-      </c>
-      <c r="C115" t="n">
-        <v>72</v>
-      </c>
-      <c r="D115" t="n">
-        <v>34</v>
-      </c>
-      <c r="E115" t="n">
-        <v>68</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>46140.85797453704</v>
-      </c>
-      <c r="B116" t="n">
-        <v>49</v>
-      </c>
-      <c r="C116" t="n">
-        <v>71</v>
-      </c>
-      <c r="D116" t="n">
-        <v>34</v>
-      </c>
-      <c r="E116" t="n">
-        <v>69</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>46141.19405092593</v>
-      </c>
-      <c r="B117" t="n">
-        <v>50</v>
-      </c>
-      <c r="C117" t="n">
-        <v>73</v>
-      </c>
-      <c r="D117" t="n">
-        <v>33</v>
-      </c>
-      <c r="E117" t="n">
-        <v>68</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>46141.37282407407</v>
-      </c>
-      <c r="B118" t="n">
-        <v>48</v>
-      </c>
-      <c r="C118" t="n">
-        <v>70</v>
-      </c>
-      <c r="D118" t="n">
-        <v>34</v>
-      </c>
-      <c r="E118" t="n">
-        <v>71</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>46141.52434027778</v>
-      </c>
-      <c r="B119" t="n">
-        <v>48</v>
-      </c>
-      <c r="C119" t="n">
-        <v>70</v>
-      </c>
-      <c r="D119" t="n">
-        <v>34</v>
-      </c>
-      <c r="E119" t="n">
-        <v>71</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>46141.69369212963</v>
-      </c>
-      <c r="B120" t="n">
-        <v>49</v>
-      </c>
-      <c r="C120" t="n">
-        <v>70</v>
-      </c>
-      <c r="D120" t="n">
-        <v>33</v>
-      </c>
-      <c r="E120" t="n">
-        <v>70</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>46141.85452546296</v>
-      </c>
-      <c r="B121" t="n">
-        <v>49</v>
-      </c>
-      <c r="C121" t="n">
-        <v>70</v>
-      </c>
-      <c r="D121" t="n">
-        <v>33</v>
-      </c>
-      <c r="E121" t="n">
-        <v>70</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>46142.09556712963</v>
-      </c>
-      <c r="B122" t="n">
-        <v>49</v>
-      </c>
-      <c r="C122" t="n">
-        <v>70</v>
-      </c>
-      <c r="D122" t="n">
-        <v>33</v>
-      </c>
-      <c r="E122" t="n">
-        <v>70</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>46142.22015046296</v>
-      </c>
-      <c r="B123" t="n">
-        <v>49</v>
-      </c>
-      <c r="C123" t="n">
-        <v>73</v>
-      </c>
-      <c r="D123" t="n">
-        <v>34</v>
-      </c>
-      <c r="E123" t="n">
-        <v>68</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>46142.35427083333</v>
-      </c>
-      <c r="B124" t="n">
-        <v>49</v>
-      </c>
-      <c r="C124" t="n">
-        <v>73</v>
-      </c>
-      <c r="D124" t="n">
-        <v>34</v>
-      </c>
-      <c r="E124" t="n">
-        <v>68</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>46142.52810185185</v>
-      </c>
-      <c r="B125" t="n">
-        <v>48</v>
-      </c>
-      <c r="C125" t="n">
-        <v>68</v>
-      </c>
-      <c r="D125" t="n">
-        <v>34</v>
-      </c>
-      <c r="E125" t="n">
-        <v>67</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>46142.70089120371</v>
-      </c>
-      <c r="B126" t="n">
-        <v>49</v>
-      </c>
-      <c r="C126" t="n">
-        <v>69</v>
-      </c>
-      <c r="D126" t="n">
-        <v>34</v>
-      </c>
-      <c r="E126" t="n">
-        <v>68</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>46142.85965277778</v>
-      </c>
-      <c r="B127" t="n">
-        <v>49</v>
-      </c>
-      <c r="C127" t="n">
-        <v>69</v>
-      </c>
-      <c r="D127" t="n">
-        <v>34</v>
-      </c>
-      <c r="E127" t="n">
-        <v>68</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>46143.02594907407</v>
-      </c>
-      <c r="B128" t="n">
-        <v>49</v>
-      </c>
-      <c r="C128" t="n">
-        <v>72</v>
-      </c>
-      <c r="D128" t="n">
-        <v>34</v>
-      </c>
-      <c r="E128" t="n">
-        <v>68</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>46143.35506944444</v>
-      </c>
-      <c r="B129" t="n">
-        <v>49</v>
-      </c>
-      <c r="C129" t="n">
-        <v>71</v>
-      </c>
-      <c r="D129" t="n">
-        <v>34</v>
-      </c>
-      <c r="E129" t="n">
-        <v>69</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>46143.52101851852</v>
-      </c>
-      <c r="B130" t="n">
-        <v>47</v>
-      </c>
-      <c r="C130" t="n">
-        <v>70</v>
-      </c>
-      <c r="D130" t="n">
-        <v>34</v>
-      </c>
-      <c r="E130" t="n">
-        <v>70</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>46143.69318287037</v>
-      </c>
-      <c r="B131" t="n">
-        <v>50</v>
-      </c>
-      <c r="C131" t="n">
-        <v>70</v>
-      </c>
-      <c r="D131" t="n">
-        <v>34</v>
-      </c>
-      <c r="E131" t="n">
-        <v>66</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>46143.86835648148</v>
-      </c>
-      <c r="B132" t="n">
-        <v>51</v>
-      </c>
-      <c r="C132" t="n">
-        <v>73</v>
-      </c>
-      <c r="D132" t="n">
-        <v>34</v>
-      </c>
-      <c r="E132" t="n">
-        <v>69</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>46144.02177083334</v>
-      </c>
-      <c r="B133" t="n">
-        <v>51</v>
-      </c>
-      <c r="C133" t="n">
-        <v>73</v>
-      </c>
-      <c r="D133" t="n">
-        <v>34</v>
-      </c>
-      <c r="E133" t="n">
-        <v>69</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>46144.18803240741</v>
-      </c>
-      <c r="B134" t="n">
-        <v>52</v>
-      </c>
-      <c r="C134" t="n">
-        <v>74</v>
-      </c>
-      <c r="D134" t="n">
-        <v>34</v>
-      </c>
-      <c r="E134" t="n">
-        <v>70</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>46144.35827546296</v>
-      </c>
-      <c r="B135" t="n">
-        <v>47</v>
-      </c>
-      <c r="C135" t="n">
-        <v>69</v>
-      </c>
-      <c r="D135" t="n">
-        <v>36</v>
-      </c>
-      <c r="E135" t="n">
-        <v>71</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>46144.52101851852</v>
-      </c>
-      <c r="B136" t="n">
-        <v>47</v>
-      </c>
-      <c r="C136" t="n">
-        <v>70</v>
-      </c>
-      <c r="D136" t="n">
-        <v>34</v>
-      </c>
-      <c r="E136" t="n">
-        <v>71</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
-        <v>46144.69450231481</v>
-      </c>
-      <c r="B137" t="n">
-        <v>51</v>
-      </c>
-      <c r="C137" t="n">
-        <v>69</v>
-      </c>
-      <c r="D137" t="n">
-        <v>34</v>
-      </c>
-      <c r="E137" t="n">
-        <v>69</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
-        <v>46144.85748842593</v>
-      </c>
-      <c r="B138" t="n">
-        <v>52</v>
-      </c>
-      <c r="C138" t="n">
-        <v>69</v>
-      </c>
-      <c r="D138" t="n">
-        <v>34</v>
-      </c>
-      <c r="E138" t="n">
-        <v>69</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>46145.06841435185</v>
-      </c>
-      <c r="B139" t="n">
-        <v>50</v>
-      </c>
-      <c r="C139" t="n">
-        <v>69</v>
-      </c>
-      <c r="D139" t="n">
-        <v>34</v>
-      </c>
-      <c r="E139" t="n">
-        <v>69</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>46145.20671296296</v>
-      </c>
-      <c r="B140" t="n">
-        <v>48</v>
-      </c>
-      <c r="C140" t="n">
-        <v>73</v>
-      </c>
-      <c r="D140" t="n">
-        <v>35</v>
-      </c>
-      <c r="E140" t="n">
-        <v>72</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="n">
-        <v>46145.35491898148</v>
-      </c>
-      <c r="B141" t="n">
-        <v>52</v>
-      </c>
-      <c r="C141" t="n">
-        <v>74</v>
-      </c>
-      <c r="D141" t="n">
-        <v>35</v>
-      </c>
-      <c r="E141" t="n">
-        <v>71</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="n">
-        <v>46145.52814814815</v>
-      </c>
-      <c r="B142" t="n">
-        <v>45</v>
-      </c>
-      <c r="C142" t="n">
-        <v>68</v>
-      </c>
-      <c r="D142" t="n">
-        <v>34</v>
-      </c>
-      <c r="E142" t="n">
-        <v>71</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="n">
-        <v>46145.85527777778</v>
-      </c>
-      <c r="B143" t="n">
-        <v>51</v>
-      </c>
-      <c r="C143" t="n">
-        <v>70</v>
-      </c>
-      <c r="D143" t="n">
-        <v>35</v>
-      </c>
-      <c r="E143" t="n">
-        <v>66</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>46146.09436342592</v>
-      </c>
-      <c r="B144" t="n">
-        <v>51</v>
-      </c>
-      <c r="C144" t="n">
-        <v>70</v>
-      </c>
-      <c r="D144" t="n">
-        <v>35</v>
-      </c>
-      <c r="E144" t="n">
-        <v>66</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>46146.21984953704</v>
-      </c>
-      <c r="B145" t="n">
-        <v>51</v>
-      </c>
-      <c r="C145" t="n">
-        <v>72</v>
-      </c>
-      <c r="D145" t="n">
-        <v>37</v>
-      </c>
-      <c r="E145" t="n">
-        <v>70</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Normal (Minor Change)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
@@ -5808,46 +4562,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sensor</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Change_Normalized</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Change_Score_Delta</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Deviation_Normalized</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Deviation_Score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Strength_Score_Fault</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RCA_Score</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Root_Cause_Suspicion</t>
         </is>
@@ -5856,113 +4610,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AssetID_9368</t>
+          <t>AssetID_9344</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.5998142341713346</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2225398660724854</v>
+        <v>0.205730545868076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4552825457439341</v>
+        <v>0.8496840908849242</v>
       </c>
       <c r="E2" t="n">
-        <v>1.043349350237618</v>
+        <v>1.766029873503918</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1492367802267725</v>
+        <v>0.1393113369127539</v>
       </c>
       <c r="G2" t="n">
-        <v>0.727641272871967</v>
+        <v>0.7247491625281295</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6190504321484442</v>
+        <v>0.623783387769937</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AssetID_9344</t>
+          <t>AssetID_9368</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2805277825879355</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1387230846230699</v>
+        <v>0.2629854362767007</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9184618420202899</v>
+        <v>0.4343823195748717</v>
       </c>
       <c r="E3" t="n">
-        <v>2.076674653340274</v>
+        <v>0.9325006559837855</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1276790845347636</v>
+        <v>0.180526082756674</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5994948123041127</v>
+        <v>0.7171911597874359</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5229518634857837</v>
+        <v>0.5877194491232942</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AssetID_9343</t>
+          <t>AssetID_9361</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.968373196798675</v>
+        <v>0.2639689279624887</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2188554196300581</v>
+        <v>0.1576808953228565</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2117177355958799</v>
+        <v>0.9648282595269422</v>
       </c>
       <c r="E4" t="n">
-        <v>0.499970828583634</v>
+        <v>1.997129366500143</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1258606478995332</v>
+        <v>0.2206148369724742</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5900454661972774</v>
+        <v>0.6143985937447154</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5157819615315059</v>
+        <v>0.4788531481496076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AssetID_9360</t>
+          <t>AssetID_9343</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2827459172424124</v>
+        <v>0.9215589291217833</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1389814919709288</v>
+        <v>0.2517628109357727</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.1060330239903658</v>
       </c>
       <c r="E5" t="n">
-        <v>2.258581406267644</v>
+        <v>0.2734889437088779</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2107179053512696</v>
+        <v>0.1763727342055533</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6413729586212062</v>
+        <v>0.5137959765560746</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5062241922315992</v>
+        <v>0.4231763753470673</v>
       </c>
     </row>
     <row r="6">
@@ -5972,109 +4726,109 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7321617049641899</v>
+        <v>0.5848704906560587</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1913373494283394</v>
+        <v>0.2035925327993453</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4552433150533241</v>
+        <v>0.4471465985803271</v>
       </c>
       <c r="E6" t="n">
-        <v>1.043261828913605</v>
+        <v>0.9581191344652628</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1732367886090501</v>
+        <v>0.2102926347208355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.593702510008757</v>
+        <v>0.5160085446181929</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4908513937857075</v>
+        <v>0.4074957482319693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AssetID_9358</t>
+          <t>AssetID_9360</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6172738940904606</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1779531960139901</v>
+        <v>0.1199146544110168</v>
       </c>
       <c r="D7" t="n">
-        <v>0.538046414499065</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.227990590584245</v>
+        <v>2.067720621680324</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1592283532526883</v>
+        <v>0.2162468793589714</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5776601542947628</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4856802791867139</v>
+        <v>0.3918765603205143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AssetID_9357</t>
+          <t>AssetID_9358</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4262056697373911</v>
+        <v>0.4117930814995392</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1556942078071432</v>
+        <v>0.1788302125480352</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5544879383085241</v>
+        <v>0.5044428849561526</v>
       </c>
       <c r="E8" t="n">
-        <v>1.264670646688786</v>
+        <v>1.073115342160212</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2035845375482461</v>
+        <v>0.1611505194651737</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4903468040229576</v>
+        <v>0.4581179832278459</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3905197766876833</v>
+        <v>0.3842920322543408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AssetID_9361</t>
+          <t>AssetID_9370</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.6025943971558497</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2061283059599847</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.1060422732246284</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.9416868986872772</v>
-      </c>
       <c r="E9" t="n">
-        <v>2.128488365466284</v>
+        <v>0.06067592526403279</v>
       </c>
       <c r="F9" t="n">
-        <v>0.17148967768238</v>
+        <v>0.1361839524303524</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4708434493436386</v>
+        <v>0.3012971985779249</v>
       </c>
       <c r="H9" t="n">
-        <v>0.390098657976838</v>
+        <v>0.2602653552193903</v>
       </c>
     </row>
     <row r="10">
@@ -6084,81 +4838,53 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1438201510859209</v>
+        <v>0.2122707237347843</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1227969746291533</v>
+        <v>0.150284392822947</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3122848354277141</v>
+        <v>0.3154071737394588</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7243300124921525</v>
+        <v>0.6937122205294654</v>
       </c>
       <c r="F10" t="n">
-        <v>0.12365551147697</v>
+        <v>0.1582776610057666</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2280524932568175</v>
+        <v>0.2638389487371215</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1998525455595475</v>
+        <v>0.2220791370487896</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AssetID_9370</t>
+          <t>AssetID_9408</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2874929591557742</v>
+        <v>0.06416288854493934</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1395345109269834</v>
+        <v>0.129094489041902</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.1343584422409145</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02764122519762795</v>
+        <v>0.3303393241824149</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06711187686538431</v>
+        <v>0.1387401774553743</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1437464795778871</v>
+        <v>0.09926066539292691</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1340993835406235</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AssetID_9408</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.01737157963859497</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1080660204364896</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.1029679402809263</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.2573565405323642</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.08280488092551568</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.06016975995976064</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0551874101509758</v>
+        <v>0.08548922306197371</v>
       </c>
     </row>
   </sheetData>
@@ -6172,68 +4898,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9358</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9359</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9360</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9361</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9368</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9369</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9370</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>AssetID_9357</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9343</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9344</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9408</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>AssetID_9358</t>
         </is>
@@ -6242,433 +4963,363 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4136578716220328</v>
+        <v>-0.2814880910122677</v>
       </c>
       <c r="D2" t="n">
-        <v>0.177486512111706</v>
+        <v>0.05201753825511685</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07517778285859036</v>
+        <v>0.2129739930321044</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0427798187178567</v>
+        <v>-0.02118478032435528</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1130970460004365</v>
+        <v>0.09278225827465289</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1673845364924884</v>
+        <v>-0.2606889405169558</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2530682169462686</v>
+        <v>-0.3966718025572403</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3766067117376183</v>
+        <v>-0.1850614430332209</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.05345671484498481</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.1068167488079185</v>
+        <v>0.1066030659264022</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>AssetID_9359</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.413657871622033</v>
+        <v>-0.2814880910122673</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08772588658859869</v>
+        <v>-0.02019388267983124</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001037140722880026</v>
+        <v>0.07463587127065635</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2162417779053431</v>
+        <v>0.1556566803042686</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3837159886804418</v>
+        <v>-0.4930957542096131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1798399291210796</v>
+        <v>0.284158399785946</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2468719311611856</v>
+        <v>0.4090829116844462</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2989656483713755</v>
+        <v>0.01086830981068994</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02303140054901041</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.06228591956144634</v>
+        <v>0.1031528944363886</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>AssetID_9360</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1774865121117059</v>
+        <v>0.05201753825511651</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08772588658859867</v>
+        <v>-0.02019388267983069</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09945659438796417</v>
+        <v>0.0454217004428924</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3159631615273557</v>
+        <v>-0.3203529510729438</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.03508442873228342</v>
+        <v>-0.07731469621525149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08534553438487304</v>
+        <v>0.1021911216855755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1049788466199092</v>
+        <v>-0.01684958410533721</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1885323921636738</v>
+        <v>0.4142106053262422</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2498420195039772</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.04539954368894749</v>
+        <v>-0.03067980991596163</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>AssetID_9361</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07517778285859042</v>
+        <v>0.2129739930321047</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.001037140722880053</v>
+        <v>0.07463587127065596</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09945659438796417</v>
+        <v>0.0454217004428924</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1851494496246698</v>
+        <v>0.261292426087168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02246240364054738</v>
+        <v>0.05605151665450944</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05703821064574031</v>
+        <v>0.07836834014915471</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2317324865774227</v>
+        <v>-0.2715137717499504</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1321377736750483</v>
+        <v>-0.3556751614837553</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1798097516595015</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.07642113845391979</v>
+        <v>0.06319527703551722</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>AssetID_9368</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04277981871785679</v>
+        <v>-0.02118478032435542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.216241777905343</v>
+        <v>0.1556566803042688</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3159631615273557</v>
+        <v>-0.3203529510729438</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1851494496246698</v>
+        <v>0.2612924260871679</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2867339183971511</v>
+        <v>-0.267707536455795</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3978122002897308</v>
+        <v>-0.6148949084538559</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1463777517906021</v>
+        <v>0.08996482461130144</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1061567520416884</v>
+        <v>0.3665223654524194</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2798444098899119</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.2483394205405445</v>
+        <v>-0.2692924537281981</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>AssetID_9369</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1130970460004364</v>
+        <v>0.09278225827465278</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3837159886804416</v>
+        <v>-0.4930957542096129</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0350844287322834</v>
+        <v>-0.07731469621525117</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02246240364054738</v>
+        <v>0.05605151665450908</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2867339183971512</v>
+        <v>-0.267707536455795</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03106116462096556</v>
+        <v>-0.03742839102365755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1209176226454808</v>
+        <v>0.2086017293705076</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1134347001148509</v>
+        <v>-0.01585136574890484</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.05093977925214002</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.07052269420723579</v>
+        <v>0.1037262874536318</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>AssetID_9370</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1673845364924884</v>
+        <v>-0.2606889405169558</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1798399291210796</v>
+        <v>0.2841583997859461</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08534553438487306</v>
+        <v>0.1021911216855756</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05703821064574029</v>
+        <v>0.07836834014915461</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3978122002897307</v>
+        <v>-0.6148949084538557</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.03106116462096559</v>
+        <v>-0.03742839102365754</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1130438241067888</v>
+        <v>0.3314261610930315</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1591796894719563</v>
+        <v>0.0598728913964577</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0657037912482191</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.1389362288879923</v>
+        <v>-0.08612559953522725</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AssetID_9357</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AssetID_9343</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.2530682169462687</v>
+        <v>-0.3966718025572402</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2468719311611856</v>
+        <v>0.409082911684446</v>
       </c>
       <c r="D9" t="n">
-        <v>0.104978846619909</v>
+        <v>-0.01684958410533741</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2317324865774224</v>
+        <v>-0.2715137717499502</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1463777517906021</v>
+        <v>0.08996482461130142</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1209176226454809</v>
+        <v>0.2086017293705074</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1130438241067887</v>
+        <v>0.3314261610930315</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2190381975553199</v>
+        <v>-0.2930961352326716</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1030131427409759</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01790005792747899</v>
+        <v>-0.2486583780174681</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AssetID_9343</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AssetID_9344</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3766067117376184</v>
+        <v>-0.1850614430332206</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2989656483713754</v>
+        <v>0.0108683098106898</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.188532392163674</v>
+        <v>0.414210605326242</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1321377736750482</v>
+        <v>-0.355675161483755</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1061567520416884</v>
+        <v>0.3665223654524194</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1134347001148509</v>
+        <v>-0.01585136574890498</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1591796894719563</v>
+        <v>0.0598728913964577</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2190381975553199</v>
+        <v>-0.2930961352326715</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3310268577108078</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.2634754734582423</v>
+        <v>-0.1504166353283235</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AssetID_9344</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AssetID_9408</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.05345671484498486</v>
+        <v>0.1066030659264023</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02303140054901042</v>
+        <v>0.1031528944363885</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2498420195039773</v>
+        <v>-0.03067980991596164</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1798097516595016</v>
+        <v>0.06319527703551725</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2798444098899119</v>
+        <v>-0.2692924537281979</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.05093977925214009</v>
+        <v>0.1037262874536318</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0657037912482191</v>
+        <v>-0.08612559953522718</v>
       </c>
       <c r="I11" t="n">
-        <v>0.103013142740976</v>
+        <v>-0.2486583780174681</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3310268577108078</v>
+        <v>-0.1504166353283236</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.05056297883116995</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AssetID_9408</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.1068167488079185</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.06228591956144632</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.04539954368894746</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.07642113845391973</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.2483394205405445</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.07052269420723578</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1389362288879923</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.01790005792747899</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.2634754734582423</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.05056297883116995</v>
-      </c>
-      <c r="L12" t="n">
         <v>0</v>
       </c>
     </row>
